--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jun-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jun-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4702.65</v>
+        <v>4769.94</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>965</v>
+        <v>978.8099999999999</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8358.91</v>
+        <v>8478.52</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1667.56</v>
+        <v>1691.42</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>870.47</v>
+        <v>882.9299999999999</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3271.33</v>
+        <v>3318.14</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8931.08</v>
+        <v>9058.879999999999</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>961.76</v>
+        <v>975.52</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3686.38</v>
+        <v>3739.13</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7666.5</v>
+        <v>7776.21</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>800.3200000000001</v>
+        <v>811.77</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1139.2</v>
+        <v>1155.51</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1762.11</v>
+        <v>1787.33</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>782.33</v>
+        <v>793.52</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2478.18</v>
+        <v>2513.64</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1119.61</v>
+        <v>1135.63</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>61368.42</v>
+        <v>62246.55</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>15244.03</v>
+        <v>15462.16</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1051.34</v>
+        <v>1066.38</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>924.48</v>
+        <v>937.71</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1423.71</v>
+        <v>1444.09</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2919.74</v>
+        <v>2961.51</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1670.02</v>
+        <v>1693.92</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>20220.71</v>
+        <v>20510.05</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1223.74</v>
+        <v>1241.25</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>898.38</v>
+        <v>911.23</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2776.83</v>
+        <v>2816.56</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>39805.84</v>
+        <v>40375.43</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2776.01</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2022.06</v>
+        <v>2045.78</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3951.81</v>
+        <v>3998.16</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3738.41</v>
+        <v>3782.26</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4412.35</v>
+        <v>4464.11</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>6358.28</v>
+        <v>6432.86</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7029.06</v>
+        <v>7111.52</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1067.31</v>
+        <v>1079.83</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2281.44</v>
+        <v>2308.2</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10119.52</v>
+        <v>10238.23</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>8905.959999999999</v>
+        <v>9010.43</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1743.66</v>
+        <v>1764.12</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4283.71</v>
+        <v>4333.96</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>981.86</v>
+        <v>998.46</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>22469.25</v>
+        <v>22849.26</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1601.27</v>
+        <v>1628.35</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>11802.41</v>
+        <v>12002.02</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8666.950000000001</v>
+        <v>8813.530000000001</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2241.09</v>
+        <v>2278.99</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>9879.52</v>
+        <v>10046.6</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3995.39</v>
+        <v>4062.97</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1452.14</v>
+        <v>1476.7</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>14522.89</v>
+        <v>14768.51</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1229.91</v>
+        <v>1250.71</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1678.15</v>
+        <v>1706.54</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1196.34</v>
+        <v>1216.57</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3240.48</v>
+        <v>3295.29</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>27984.42</v>
+        <v>28457.7</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3015.75</v>
+        <v>3066.76</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1535.37</v>
+        <v>1561.34</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>844.84</v>
+        <v>853.4299999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>15271.42</v>
+        <v>15426.72</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>15593.27</v>
+        <v>15751.84</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>941.77</v>
+        <v>951.34</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>15975.78</v>
+        <v>16138.25</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1323.86</v>
+        <v>1337.33</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3003.53</v>
+        <v>3034.07</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1180.96</v>
+        <v>1192.97</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2293.23</v>
+        <v>2316.55</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5934.81</v>
+        <v>5995.16</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>925.6900000000001</v>
+        <v>935.11</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8912.23</v>
+        <v>9002.860000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3582.4</v>
+        <v>3618.83</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>22518.05</v>
+        <v>22747.05</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>27638.79</v>
+        <v>27898.02</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4712.24</v>
+        <v>4756.44</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>4972.53</v>
+        <v>5019.16</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>9962.540000000001</v>
+        <v>10055.98</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1090.55</v>
+        <v>1100.78</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8815.450000000001</v>
+        <v>8898.129999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>855.4</v>
+        <v>863.42</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3585.08</v>
+        <v>3618.7</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>941.53</v>
+        <v>950.36</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>11399.12</v>
+        <v>11506.03</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2033.99</v>
+        <v>2053.07</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>6444.84</v>
+        <v>6505.28</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>857.53</v>
+        <v>851.02</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1739.19</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1369.96</v>
+        <v>1359.57</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1810.59</v>
+        <v>1796.85</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>13103.36</v>
+        <v>13003.95</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1011.03</v>
+        <v>1003.36</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5089.09</v>
+        <v>5050.48</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2165.99</v>
+        <v>2149.55</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>4306.94</v>
+        <v>4274.27</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>44590.69</v>
+        <v>44252.41</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1059.97</v>
+        <v>1051.93</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>46491.84</v>
+        <v>46139.14</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>12606.26</v>
+        <v>12510.63</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3999.66</v>
+        <v>3969.32</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>962.73</v>
+        <v>955.42</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>11482.69</v>
+        <v>11395.57</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>6888.79</v>
+        <v>6772.4</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2696.08</v>
+        <v>2650.53</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>13791.67</v>
+        <v>13558.65</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1773.87</v>
+        <v>1743.9</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>6258.4</v>
+        <v>6152.66</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1318.57</v>
+        <v>1296.29</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1200.95</v>
+        <v>1180.66</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>6293.12</v>
+        <v>6203.81</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2406.6</v>
+        <v>2372.45</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>6516.46</v>
+        <v>6423.98</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>11176.76</v>
+        <v>11018.14</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>9877.41</v>
+        <v>9737.23</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>8823.879999999999</v>
+        <v>8698.65</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>4327.7</v>
+        <v>4266.28</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>7061.32</v>
+        <v>6961.1</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4675.44</v>
+        <v>4609.09</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1228.29</v>
+        <v>1210.86</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1199.64</v>
+        <v>1182.61</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5791.71</v>
+        <v>5709.51</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>8997.719999999999</v>
+        <v>8870.02</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>787.89</v>
+        <v>776.71</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>60664.03</v>
+        <v>59803.07</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>985.46</v>
+        <v>971.48</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1646.45</v>
+        <v>1623.83</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2907.41</v>
+        <v>2867.46</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>4424.5</v>
+        <v>4363.71</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2164.93</v>
+        <v>2135.18</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>894.75</v>
+        <v>882.46</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>809.48</v>
+        <v>798.36</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>897.72</v>
+        <v>885.38</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>10546.73</v>
+        <v>10401.82</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1951.14</v>
+        <v>1924.33</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1757.81</v>
+        <v>1733.66</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1475.05</v>
+        <v>1454.78</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3751.29</v>
+        <v>3699.75</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>968.59</v>
+        <v>955.28</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4982.03</v>
+        <v>4913.58</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1162.39</v>
+        <v>1146.42</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>798.48</v>
+        <v>787.51</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>5335.7</v>
+        <v>5262.38</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1324.58</v>
+        <v>1316.37</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>795.51</v>
+        <v>790.58</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>8123.09</v>
+        <v>8072.73</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>4833.06</v>
+        <v>4803.1</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2007.52</v>
+        <v>1995.07</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2696.28</v>
+        <v>2679.56</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1064.14</v>
+        <v>1057.55</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1203.26</v>
+        <v>1195.8</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3246.19</v>
+        <v>3226.06</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1829.34</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>6310.52</v>
+        <v>6271.4</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>11623.4</v>
+        <v>11551.34</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>919.89</v>
+        <v>914.1799999999999</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>10274.7</v>
+        <v>10321.36</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>27662.65</v>
+        <v>27788.28</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1685.79</v>
+        <v>1693.44</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>970.17</v>
+        <v>974.5700000000001</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1756.24</v>
+        <v>1764.21</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>4443.24</v>
+        <v>4463.42</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3024.44</v>
+        <v>3038.18</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>957.84</v>
+        <v>962.1900000000001</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>17691.12</v>
+        <v>17771.47</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1545.16</v>
+        <v>1552.17</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>810.63</v>
+        <v>814.3200000000001</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2178.63</v>
+        <v>2188.52</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>10221.01</v>
+        <v>10267.43</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>3531.64</v>
+        <v>3547.68</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2181.26</v>
+        <v>2191.17</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>3984.9</v>
+        <v>4002.99</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>9634.67</v>
+        <v>9678.42</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2694.34</v>
+        <v>2706.58</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>4201.96</v>
+        <v>4264.52</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1256.67</v>
+        <v>1275.39</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>5125.24</v>
+        <v>5201.56</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>906.6900000000001</v>
+        <v>920.1900000000001</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>7648.72</v>
+        <v>7762.61</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>27089.03</v>
+        <v>27492.4</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>18370.89</v>
+        <v>18644.44</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3503.5</v>
+        <v>3555.66</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>18094.33</v>
+        <v>18363.76</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1947.68</v>
+        <v>1976.68</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2361.86</v>
+        <v>2397.03</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>931.16</v>
+        <v>945.03</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>4770.04</v>
+        <v>4841.07</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>22990.69</v>
+        <v>23333.03</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1774.71</v>
+        <v>1801.13</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>7255.18</v>
+        <v>7363.21</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>7532.09</v>
+        <v>7644.25</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>8890.559999999999</v>
+        <v>9059.59</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>14363.82</v>
+        <v>14636.89</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>4370.85</v>
+        <v>4453.95</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>7271.31</v>
+        <v>7409.55</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1506.44</v>
+        <v>1535.08</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1045.82</v>
+        <v>1065.7</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2151.1</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2510.95</v>
+        <v>2558.69</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3273.41</v>
+        <v>3335.65</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>16867.36</v>
+        <v>17188.03</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>3084.78</v>
+        <v>3143.43</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3990.01</v>
+        <v>4065.86</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1136.86</v>
+        <v>1158.47</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>6116.4</v>
+        <v>6232.69</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>8002.44</v>
+        <v>8154.58</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3398.03</v>
+        <v>3462.63</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2102.48</v>
+        <v>2142.45</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>935.71</v>
+        <v>953.5</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>4111.78</v>
+        <v>4189.95</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>5265.81</v>
+        <v>5365.92</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1818.68</v>
+        <v>1853.26</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>38425.79</v>
+        <v>39156.32</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>3821.64</v>
+        <v>3894.3</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>4116.72</v>
+        <v>4194.99</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2940.66</v>
+        <v>2996.57</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>9662.85</v>
+        <v>9846.559999999999</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>858.64</v>
+        <v>874.97</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>4904.32</v>
+        <v>4997.56</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>3766.29</v>
+        <v>3837.9</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>854.1900000000001</v>
+        <v>870.4299999999999</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>12675.78</v>
+        <v>12916.76</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2722.27</v>
+        <v>2774.02</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1603.17</v>
+        <v>1639.32</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>26916.88</v>
+        <v>27523.93</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1223.74</v>
+        <v>1251.34</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>64822.91</v>
+        <v>66284.83</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1946.29</v>
+        <v>1990.18</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>15275.93</v>
+        <v>15620.45</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>836.79</v>
+        <v>855.66</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1371.65</v>
+        <v>1402.59</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>16182.96</v>
+        <v>16547.93</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>8659.459999999999</v>
+        <v>8854.76</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1112.48</v>
+        <v>1137.57</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1632.36</v>
+        <v>1669.17</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>793.08</v>
+        <v>810.96</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1405.7</v>
+        <v>1437.4</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>796.02</v>
+        <v>813.97</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>39582.72</v>
+        <v>40475.42</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1996.55</v>
+        <v>2041.57</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>820.71</v>
+        <v>839.22</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1875.43</v>
+        <v>1917.72</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2247.64</v>
+        <v>2298.33</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1349.17</v>
+        <v>1379.6</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>9338.049999999999</v>
+        <v>9548.65</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2709.58</v>
+        <v>2770.69</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>802.21</v>
+        <v>820.3</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>7999.72</v>
+        <v>8180.14</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>7812.32</v>
+        <v>7988.51</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>46780.65</v>
+        <v>47835.67</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1801.37</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>9508.77</v>
+        <v>9723.219999999999</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>794.34</v>
+        <v>812.26</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2042.59</v>
+        <v>2088.66</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1035.37</v>
+        <v>1058.72</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2756.74</v>
+        <v>2818.91</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>7860.31</v>
+        <v>7914.58</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2475.13</v>
+        <v>2492.22</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1080.04</v>
+        <v>1087.49</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>5545.7</v>
+        <v>5583.99</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>3042.89</v>
+        <v>3063.9</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1204.62</v>
+        <v>1212.93</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1541.2</v>
+        <v>1551.85</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>20189.73</v>
+        <v>20329.12</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>4663.13</v>
+        <v>4695.33</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>877.36</v>
+        <v>883.42</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>5209.43</v>
+        <v>5245.4</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1107.25</v>
+        <v>1114.9</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1060.58</v>
+        <v>1067.91</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>791.86</v>
+        <v>797.33</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1990.11</v>
+        <v>2003.85</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>944.75</v>
+        <v>951.27</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2729.07</v>
+        <v>2747.91</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>3701.31</v>
+        <v>3726.87</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>41804.51</v>
+        <v>42093.14</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1106.76</v>
+        <v>1114.4</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>2605.56</v>
+        <v>2613.61</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1975.38</v>
+        <v>1981.48</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2207.23</v>
+        <v>2214.06</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>19218.49</v>
+        <v>19277.91</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>14929.01</v>
+        <v>14975.16</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>9224.639999999999</v>
+        <v>9253.16</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1174.26</v>
+        <v>1177.89</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>4492.26</v>
+        <v>4506.15</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>24052.11</v>
+        <v>24126.47</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>43108.4</v>
+        <v>43241.67</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>5706.41</v>
+        <v>5724.05</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1225.05</v>
+        <v>1221.81</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>797.1799999999999</v>
+        <v>795.0700000000001</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>11201.95</v>
+        <v>11172.32</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2806.44</v>
+        <v>2799.02</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1019.19</v>
+        <v>1016.49</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1316.27</v>
+        <v>1312.79</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1166.84</v>
+        <v>1163.75</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>816.79</v>
+        <v>814.63</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>2207</v>
+        <v>2201.17</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>10990.67</v>
+        <v>10961.6</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1941.61</v>
+        <v>1936.48</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1149.32</v>
+        <v>1146.28</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>6256.74</v>
+        <v>6240.19</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>3545.72</v>
+        <v>3536.34</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2842.17</v>
+        <v>2834.65</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>7574.3</v>
+        <v>7554.26</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3351.79</v>
+        <v>3342.92</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>26039.71</v>
+        <v>25970.83</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>2281.27</v>
+        <v>2250.88</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2051.09</v>
+        <v>2023.77</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>20541.49</v>
+        <v>20267.87</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1144.75</v>
+        <v>1129.5</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>855.3</v>
+        <v>843.91</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>4239.53</v>
+        <v>4183.06</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>847.61</v>
+        <v>836.3200000000001</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>10385.35</v>
+        <v>10247.01</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>12967.39</v>
+        <v>12794.66</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1106.76</v>
+        <v>1092.02</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>1924.52</v>
+        <v>1898.89</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>3810.05</v>
+        <v>3759.3</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2618.48</v>
+        <v>2583.61</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>791.67</v>
+        <v>781.13</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>22908.7</v>
+        <v>22603.55</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>4470.85</v>
+        <v>4383.34</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>2476.54</v>
+        <v>2428.06</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>3451.87</v>
+        <v>3384.31</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>895.46</v>
+        <v>877.9400000000001</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>3769.87</v>
+        <v>3696.08</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>61772.08</v>
+        <v>60562.97</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2062.25</v>
+        <v>2021.88</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>2952.71</v>
+        <v>2894.92</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>33776.88</v>
+        <v>33115.74</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1560.33</v>
+        <v>1529.79</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>5136.86</v>
+        <v>5036.31</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2885.4</v>
+        <v>2828.92</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>1271.55</v>
+        <v>1246.66</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1012.56</v>
+        <v>992.74</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1399.18</v>
+        <v>1371.79</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1049.62</v>
+        <v>1029.08</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1025.31</v>
+        <v>1005.24</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>1389.84</v>
+        <v>1362.63</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>3635.34</v>
+        <v>3564.18</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>874.4</v>
+        <v>857.28</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1695.73</v>
+        <v>1662.54</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>18596.74</v>
+        <v>18321.21</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>1351.46</v>
+        <v>1331.44</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>2449.33</v>
+        <v>2413.05</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>8778.809999999999</v>
+        <v>8648.74</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>3579.19</v>
+        <v>3526.16</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>14857.76</v>
+        <v>14637.63</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>5137.35</v>
+        <v>5061.23</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>798.02</v>
+        <v>786.2</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>3110.08</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1415.21</v>
+        <v>1394.24</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>19118.31</v>
+        <v>18835.06</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>3962.34</v>
+        <v>3903.64</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>1147.01</v>
+        <v>1130.02</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1086.75</v>
+        <v>1070.65</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1248.88</v>
+        <v>1230.38</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>2077.2</v>
+        <v>2046.42</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>15123.56</v>
+        <v>14812.75</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>7729.13</v>
+        <v>7570.28</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>1028.92</v>
+        <v>1007.78</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>865.33</v>
+        <v>847.54</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1735.36</v>
+        <v>1699.69</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>61057.82</v>
+        <v>59802.97</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>9736.9</v>
+        <v>9536.790000000001</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1654.62</v>
+        <v>1620.62</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>13040.96</v>
+        <v>12772.95</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>4680.2</v>
+        <v>4584.01</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jun-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jun-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jun-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.303.388-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1058,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1123,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1554,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1680,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2050,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2176,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2241,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2306,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2371,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2619,11 @@
           <t>77.714.558-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3111,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3176,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3241,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3367,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3554,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3741,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3928,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4054,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4241,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4306,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4432,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4619,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4684,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4871,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4936,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5184,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5310,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5741,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5928,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6115,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6180,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6550,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6737,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6863,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +6989,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7054,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7485,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7611,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7676,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7863,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7928,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8054,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8180,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8367,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8493,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8863,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +8989,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9176,11 @@
           <t>76.193.188-1</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9363,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9489,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9554,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9802,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9867,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9932,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +9997,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10245,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10615,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +10985,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11111,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11359,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11424,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11489,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11554,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11741,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11867,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12176,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12302,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12367,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12493,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12558,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12623,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12749,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12814,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12879,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +12944,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13009,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13196,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13261,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13387,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13818,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13883,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +13948,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14074,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14200,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14692,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14818,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +14944,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15009,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15074,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15200,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15265,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15330,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15517,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15582,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15647,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +15956,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16082,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16269,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16334,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16399,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16464,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16590,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16716,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +16842,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +16907,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +16972,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17098,11 @@
           <t>77.724.409-4</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17163,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17228,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17354,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17419,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17484,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17610,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17675,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +17740,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18049,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18114,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18240,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18610,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18675,11 @@
           <t>76.698.741-9</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +18923,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +18988,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19114,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19179,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19366,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19431,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19496,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19561,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +19870,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20057,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20183,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20309,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20374,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20561,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20748,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +20813,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +20878,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +20943,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21191,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21317,11 @@
           <t>76.698.741-9</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21382,11 @@
           <t>76.698.741-9</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21569,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21634,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +21699,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21764,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +21829,11 @@
           <t>76.698.741-9</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +21955,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22203,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22512,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22577,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22703,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +22890,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +22955,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23081,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23146,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23455,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jun-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jun-2026.xlsx
@@ -7802,7 +7802,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20626,7 +20630,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22142,7 +22150,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jun-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jun-2026.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -20285,7 +20285,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -21427,7 +21427,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -21549,7 +21549,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -21614,7 +21614,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -21809,7 +21809,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -22122,7 +22122,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -23004,7 +23004,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -23378,7 +23378,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
